--- a/results/feature_selection/global/wrapper/qP_calc/metrics_global.xlsx
+++ b/results/feature_selection/global/wrapper/qP_calc/metrics_global.xlsx
@@ -492,153 +492,153 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>t, P, I, FS_calc, Plag1, mu_calc</t>
+          <t>t, t_ind_ad, P, I, FS_calc, Plag1, X_calc, V_calc, mu_calc, dVdt_calc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.8439827753949747</v>
+        <v>0.9227498106827063</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000658429767062613</v>
+        <v>0.0006000821531228148</v>
       </c>
       <c r="F2" t="n">
-        <v>3.124628247400633e-06</v>
+        <v>1.869591465747777e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001767661802325499</v>
+        <v>0.00136733005004197</v>
       </c>
       <c r="H2" t="n">
-        <v>368.4668507259437</v>
+        <v>309.1603614043058</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04980735462128079</v>
+        <v>0.02817636550921413</v>
       </c>
       <c r="J2" t="n">
-        <v>-1940.134067373353</v>
+        <v>-1641.91361792846</v>
       </c>
       <c r="K2" t="n">
-        <v>-1921.912351758871</v>
+        <v>-1613.550798858945</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>poisson</t>
+          <t>Ridge_b</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>t, t_ind, P, I, mu_calc</t>
+          <t>t, P, Plag1</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.826899587432279</v>
+        <v>0.8952118793425505</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0007359812426545007</v>
+        <v>0.0008080984147394094</v>
       </c>
       <c r="F3" t="n">
-        <v>3.466761058691357e-06</v>
+        <v>2.536058200300853e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001861924020654806</v>
+        <v>0.00159250061233924</v>
       </c>
       <c r="H3" t="n">
-        <v>401.6726009254817</v>
+        <v>321.295807496895</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0544325505030574</v>
+        <v>0.03293821143797505</v>
       </c>
       <c r="J3" t="n">
-        <v>-1926.132631107611</v>
+        <v>-1617.497346072906</v>
       </c>
       <c r="K3" t="n">
-        <v>-1910.947868095543</v>
+        <v>-1608.988500352051</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ridge_b</t>
+          <t>elasticnet_b</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>t, P, I, Plag1, mu_calc</t>
+          <t>t, P, Plag1</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7989285473031685</v>
+        <v>0.8826748220755998</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001102310345621762</v>
+        <v>0.0008443223114411007</v>
       </c>
       <c r="F4" t="n">
-        <v>4.02694986039486e-06</v>
+        <v>2.839477201328918e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002006726154809086</v>
+        <v>0.001685074835527763</v>
       </c>
       <c r="H4" t="n">
-        <v>462.6609804926708</v>
+        <v>384.9465624638009</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06282425467395172</v>
+        <v>0.036699541011361</v>
       </c>
       <c r="J4" t="n">
-        <v>-1903.065204362691</v>
+        <v>-1603.258216453753</v>
       </c>
       <c r="K4" t="n">
-        <v>-1887.880441350623</v>
+        <v>-1594.749370732899</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>elasticnet_b</t>
+          <t>LASSO_b</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>t, P, I, Plag1, mu_calc</t>
+          <t>t, P, Plag1, mu_calc</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7788552237494311</v>
+        <v>0.8172773536024351</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001122735556668058</v>
+        <v>0.001010793271088896</v>
       </c>
       <c r="F5" t="n">
-        <v>4.428967483474665e-06</v>
+        <v>4.422211820097894e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002104511221988294</v>
+        <v>0.002102905566138883</v>
       </c>
       <c r="H5" t="n">
-        <v>452.5832404748635</v>
+        <v>995.9072823487622</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06884653315240913</v>
+        <v>0.05681988946754354</v>
       </c>
       <c r="J5" t="n">
-        <v>-1888.410987516255</v>
+        <v>-1545.437692481757</v>
       </c>
       <c r="K5" t="n">
-        <v>-1873.226224504187</v>
+        <v>-1534.092564853951</v>
       </c>
     </row>
     <row r="6">
@@ -648,198 +648,198 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>t, P, I</t>
+          <t>P, I, Plag1, V_calc</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.7195154671537083</v>
+        <v>0.8102186849150967</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0009336748590677647</v>
+        <v>0.0007184476242832293</v>
       </c>
       <c r="F6" t="n">
-        <v>5.617391903421062e-06</v>
+        <v>4.593044110012227e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002370103774821065</v>
+        <v>0.002143138845248303</v>
       </c>
       <c r="H6" t="n">
-        <v>392.9323368372667</v>
+        <v>380.3474482018723</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08564929202821991</v>
+        <v>0.058937609656348</v>
       </c>
       <c r="J6" t="n">
-        <v>-1855.80503368841</v>
+        <v>-1540.661911163824</v>
       </c>
       <c r="K6" t="n">
-        <v>-1846.694175881169</v>
+        <v>-1529.316783536019</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LASSO_b</t>
+          <t>rf_b</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>t, P, I, Plag1, mu_calc</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.4716524058056498</v>
+        <v>0.8101466954773805</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001347724116347103</v>
+        <v>0.0009817834846827021</v>
       </c>
       <c r="F7" t="n">
-        <v>1.058145869114928e-05</v>
+        <v>4.594786381967384e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>0.003252915414078466</v>
+        <v>0.002143545283395568</v>
       </c>
       <c r="H7" t="n">
-        <v>418.3483832938555</v>
+        <v>922.5052619436017</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1610116852793889</v>
+        <v>0.05745920770725324</v>
       </c>
       <c r="J7" t="n">
-        <v>-1754.286719353355</v>
+        <v>-1546.614124851447</v>
       </c>
       <c r="K7" t="n">
-        <v>-1739.101956341287</v>
+        <v>-1543.777842944495</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>poisson</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>P, T, I</t>
+          <t>t_ind_ad, P, I, mu_calc</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.202530960986973</v>
+        <v>0.7788939651651732</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001776853744312119</v>
+        <v>0.001030483910368365</v>
       </c>
       <c r="F8" t="n">
-        <v>1.597127683841187e-05</v>
+        <v>5.351157834120439e-06</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003996407991986287</v>
+        <v>0.002313256975374859</v>
       </c>
       <c r="H8" t="n">
-        <v>993.7576286101969</v>
+        <v>992.1680325189805</v>
       </c>
       <c r="I8" t="n">
-        <v>0.240751891597695</v>
+        <v>0.06833555626093195</v>
       </c>
       <c r="J8" t="n">
-        <v>-1694.886671579795</v>
+        <v>-1521.412897962711</v>
       </c>
       <c r="K8" t="n">
-        <v>-1685.775813772554</v>
+        <v>-1510.067770334906</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>rf_b</t>
+          <t>linear</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>P, I</t>
+          <t>P, T, mu_calc</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.1765621923329606</v>
+        <v>0.7515614876809791</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00159629372061624</v>
+        <v>0.001254962787639884</v>
       </c>
       <c r="F9" t="n">
-        <v>1.649136523436918e-05</v>
+        <v>6.012652221303162e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>0.004060956197051278</v>
+        <v>0.002452071006578554</v>
       </c>
       <c r="H9" t="n">
-        <v>951.7967101631459</v>
+        <v>1455.827285648282</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2480428862557759</v>
+        <v>0.0760357625522612</v>
       </c>
       <c r="J9" t="n">
-        <v>-1691.951739507584</v>
+        <v>-1508.727220277932</v>
       </c>
       <c r="K9" t="n">
-        <v>-1685.877834302756</v>
+        <v>-1500.218374557078</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>svm_rbf</t>
+          <t>svm_linear</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>P, I</t>
+          <t>t_ind_ad, P, Plag1, Xlag1_calc</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.2007537745889985</v>
+        <v>-0.3921741192858967</v>
       </c>
       <c r="E10" t="n">
-        <v>0.003400135167999717</v>
+        <v>0.005175317243000892</v>
       </c>
       <c r="F10" t="n">
-        <v>2.404804451400855e-05</v>
+        <v>3.369308056400016e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.004903880556662096</v>
+        <v>0.005804574107029745</v>
       </c>
       <c r="H10" t="n">
-        <v>1192.825567020125</v>
+        <v>3639.91526651797</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7224859320157188</v>
+        <v>0.8393516418843278</v>
       </c>
       <c r="J10" t="n">
-        <v>-1633.860358581695</v>
+        <v>-1289.575476340986</v>
       </c>
       <c r="K10" t="n">
-        <v>-1627.786453376867</v>
+        <v>-1278.23034871318</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>svm_poly</t>
+          <t>svm_rbf</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -847,38 +847,38 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>P, I</t>
+          <t>P, Plag1</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.6226057763476718</v>
+        <v>-0.5485338585473836</v>
       </c>
       <c r="E11" t="n">
-        <v>0.004572080602999444</v>
+        <v>0.005642416564939481</v>
       </c>
       <c r="F11" t="n">
-        <v>3.249666731354011e-05</v>
+        <v>3.747726331737991e-05</v>
       </c>
       <c r="G11" t="n">
-        <v>0.005700584822063444</v>
+        <v>0.006121867633114906</v>
       </c>
       <c r="H11" t="n">
-        <v>1357.776694738483</v>
+        <v>3609.870372125369</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9756089611428421</v>
+        <v>0.9311727832970746</v>
       </c>
       <c r="J11" t="n">
-        <v>-1587.493444785146</v>
+        <v>-1280.163791171107</v>
       </c>
       <c r="K11" t="n">
-        <v>-1581.419539580319</v>
+        <v>-1274.491227357204</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>svm_linear</t>
+          <t>svm_poly</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -886,32 +886,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>P, I</t>
+          <t>P, Plag1</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-1.130446038726702</v>
+        <v>-2.43123429265257</v>
       </c>
       <c r="E12" t="n">
-        <v>0.005731222342014629</v>
+        <v>0.008871791591213084</v>
       </c>
       <c r="F12" t="n">
-        <v>4.266741629983989e-05</v>
+        <v>8.304194989316687e-05</v>
       </c>
       <c r="G12" t="n">
-        <v>0.006532030029006288</v>
+        <v>0.009112735587800564</v>
       </c>
       <c r="H12" t="n">
-        <v>1179.471032729185</v>
+        <v>4238.389887134308</v>
       </c>
       <c r="I12" t="n">
-        <v>1.280327357618841</v>
+        <v>2.060856834321392</v>
       </c>
       <c r="J12" t="n">
-        <v>-1545.5595520543</v>
+        <v>-1179.916746838693</v>
       </c>
       <c r="K12" t="n">
-        <v>-1539.485646849473</v>
+        <v>-1174.24418302479</v>
       </c>
     </row>
   </sheetData>

--- a/results/feature_selection/global/wrapper/qP_calc/metrics_global.xlsx
+++ b/results/feature_selection/global/wrapper/qP_calc/metrics_global.xlsx
@@ -488,124 +488,124 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>tweedie</t>
+          <t>knn</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>t, t_ind_ad, P, I, FS_calc, Plag1, X_calc, V_calc, mu_calc, dVdt_calc</t>
+          <t>t, t_ind, t_ind_ad, T, I, X_calc, V_calc, dXdt_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.9227498106827063</v>
+        <v>0.810998545093071</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0006000821531228148</v>
+        <v>0.0007234786044292191</v>
       </c>
       <c r="F2" t="n">
-        <v>1.869591465747777e-06</v>
+        <v>4.574170111823968e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00136733005004197</v>
+        <v>0.002138730958260989</v>
       </c>
       <c r="H2" t="n">
-        <v>309.1603614043058</v>
+        <v>520.1446837301559</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02817636550921413</v>
+        <v>0.06120363839115698</v>
       </c>
       <c r="J2" t="n">
-        <v>-1641.91361792846</v>
+        <v>-1531.180744273729</v>
       </c>
       <c r="K2" t="n">
-        <v>-1613.550798858945</v>
+        <v>-1505.654207111166</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ridge_b</t>
+          <t>tweedie</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>t, P, Plag1</t>
+          <t>t_ind, t_ind_ad, I, X_calc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.8952118793425505</v>
+        <v>0.8065244737030708</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0008080984147394094</v>
+        <v>0.00085980535804047</v>
       </c>
       <c r="F3" t="n">
-        <v>2.536058200300853e-06</v>
+        <v>4.68245056733889e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00159250061233924</v>
+        <v>0.002163897078730615</v>
       </c>
       <c r="H3" t="n">
-        <v>321.295807496895</v>
+        <v>669.6561486172901</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03293821143797505</v>
+        <v>0.06004593560447592</v>
       </c>
       <c r="J3" t="n">
-        <v>-1617.497346072906</v>
+        <v>-1538.232808906948</v>
       </c>
       <c r="K3" t="n">
-        <v>-1608.988500352051</v>
+        <v>-1526.887681279142</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>elasticnet_b</t>
+          <t>poisson</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>t, P, Plag1</t>
+          <t>t_ind_ad, T, I, V_calc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8826748220755998</v>
+        <v>0.4237192234819377</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0008443223114411007</v>
+        <v>0.001426906154968586</v>
       </c>
       <c r="F4" t="n">
-        <v>2.839477201328918e-06</v>
+        <v>1.394701593839947e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001685074835527763</v>
+        <v>0.003734570382038538</v>
       </c>
       <c r="H4" t="n">
-        <v>384.9465624638009</v>
+        <v>1175.907142576187</v>
       </c>
       <c r="I4" t="n">
-        <v>0.036699541011361</v>
+        <v>0.1748939958665756</v>
       </c>
       <c r="J4" t="n">
-        <v>-1603.258216453753</v>
+        <v>-1400.710867959432</v>
       </c>
       <c r="K4" t="n">
-        <v>-1594.749370732899</v>
+        <v>-1389.365740331626</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LASSO_b</t>
+          <t>rf_b</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -613,149 +613,149 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>t, P, Plag1, mu_calc</t>
+          <t>t, t_ind, t_ind_ad, mu_calc</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.8172773536024351</v>
+        <v>0.3630792019840874</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001010793271088896</v>
+        <v>0.001207449833222983</v>
       </c>
       <c r="F5" t="n">
-        <v>4.422211820097894e-06</v>
+        <v>1.541461191035863e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002102905566138883</v>
+        <v>0.003926144662433954</v>
       </c>
       <c r="H5" t="n">
-        <v>995.9072823487622</v>
+        <v>626.9897101231327</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05681988946754354</v>
+        <v>0.1930870296331111</v>
       </c>
       <c r="J5" t="n">
-        <v>-1545.437692481757</v>
+        <v>-1388.104528803918</v>
       </c>
       <c r="K5" t="n">
-        <v>-1534.092564853951</v>
+        <v>-1376.759401176112</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>knn</t>
+          <t>Ridge_b</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>P, I, Plag1, V_calc</t>
+          <t>t, t_ind, t_ind_ad, X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.8102186849150967</v>
+        <v>0.3614793866229301</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0007184476242832293</v>
+        <v>0.002345261003869446</v>
       </c>
       <c r="F6" t="n">
-        <v>4.593044110012227e-06</v>
+        <v>1.545333027690796e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002143138845248303</v>
+        <v>0.003931072407996062</v>
       </c>
       <c r="H6" t="n">
-        <v>380.3474482018723</v>
+        <v>1152.11648947025</v>
       </c>
       <c r="I6" t="n">
-        <v>0.058937609656348</v>
+        <v>0.1955670013443148</v>
       </c>
       <c r="J6" t="n">
-        <v>-1540.661911163824</v>
+        <v>-1379.788439269078</v>
       </c>
       <c r="K6" t="n">
-        <v>-1529.316783536019</v>
+        <v>-1357.098184013467</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf_b</t>
+          <t>elasticnet_b</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>t_ind, t_ind_ad, X_calc, V_calc, mu_calc, dXdt_calc</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.8101466954773805</v>
+        <v>0.3402792871388413</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0009817834846827021</v>
+        <v>0.002287970419760139</v>
       </c>
       <c r="F7" t="n">
-        <v>4.594786381967384e-06</v>
+        <v>1.596641025015772e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002143545283395568</v>
+        <v>0.003995799075298672</v>
       </c>
       <c r="H7" t="n">
-        <v>922.5052619436017</v>
+        <v>1016.330923072539</v>
       </c>
       <c r="I7" t="n">
-        <v>0.05745920770725324</v>
+        <v>0.2009273903455228</v>
       </c>
       <c r="J7" t="n">
-        <v>-1546.614124851447</v>
+        <v>-1379.672948631027</v>
       </c>
       <c r="K7" t="n">
-        <v>-1543.777842944495</v>
+        <v>-1362.655257189318</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>poisson</t>
+          <t>LASSO_b</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>t_ind_ad, P, I, mu_calc</t>
+          <t>t_ind_ad, T, V_calc</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.7788939651651732</v>
+        <v>0.2716058446729253</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001030483910368365</v>
+        <v>0.002047136111397037</v>
       </c>
       <c r="F8" t="n">
-        <v>5.351157834120439e-06</v>
+        <v>1.762842924444716e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002313256975374859</v>
+        <v>0.004198622303142683</v>
       </c>
       <c r="H8" t="n">
-        <v>992.1680325189805</v>
+        <v>1125.188787539786</v>
       </c>
       <c r="I8" t="n">
-        <v>0.06833555626093195</v>
+        <v>0.2200305864985936</v>
       </c>
       <c r="J8" t="n">
-        <v>-1521.412897962711</v>
+        <v>-1373.195705302484</v>
       </c>
       <c r="K8" t="n">
-        <v>-1510.067770334906</v>
+        <v>-1364.68685958163</v>
       </c>
     </row>
     <row r="9">
@@ -765,114 +765,114 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>P, T, mu_calc</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.7515614876809791</v>
+        <v>0.01562942248896027</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001254962787639884</v>
+        <v>0.002014507690724158</v>
       </c>
       <c r="F9" t="n">
-        <v>6.012652221303162e-06</v>
+        <v>2.382351224135906e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002452071006578554</v>
+        <v>0.004880933541993689</v>
       </c>
       <c r="H9" t="n">
-        <v>1455.827285648282</v>
+        <v>1979.334579210555</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0760357625522612</v>
+        <v>0.2958278497118809</v>
       </c>
       <c r="J9" t="n">
-        <v>-1508.727220277932</v>
+        <v>-1339.249532011558</v>
       </c>
       <c r="K9" t="n">
-        <v>-1500.218374557078</v>
+        <v>-1336.413250104607</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>svm_linear</t>
+          <t>svm_rbf</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>t_ind_ad, P, Plag1, Xlag1_calc</t>
+          <t>t, t_ind_ad</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.3921741192858967</v>
+        <v>-0.007699272210740071</v>
       </c>
       <c r="E10" t="n">
-        <v>0.005175317243000892</v>
+        <v>0.003591133369350678</v>
       </c>
       <c r="F10" t="n">
-        <v>3.369308056400016e-05</v>
+        <v>2.438810799061286e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.005804574107029745</v>
+        <v>0.004938431733922507</v>
       </c>
       <c r="H10" t="n">
-        <v>3639.91526651797</v>
+        <v>2799.88878686078</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8393516418843278</v>
+        <v>0.6066537066776311</v>
       </c>
       <c r="J10" t="n">
-        <v>-1289.575476340986</v>
+        <v>-1334.298280160157</v>
       </c>
       <c r="K10" t="n">
-        <v>-1278.23034871318</v>
+        <v>-1328.625716346254</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>svm_rbf</t>
+          <t>svm_linear</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>P, Plag1</t>
+          <t>t, t_ind, t_ind_ad, X_calc, V_calc, mu_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.5485338585473836</v>
+        <v>-0.07371657271770093</v>
       </c>
       <c r="E11" t="n">
-        <v>0.005642416564939481</v>
+        <v>0.003893150879675575</v>
       </c>
       <c r="F11" t="n">
-        <v>3.747726331737991e-05</v>
+        <v>2.598584364291746e-05</v>
       </c>
       <c r="G11" t="n">
-        <v>0.006121867633114906</v>
+        <v>0.005097631179569336</v>
       </c>
       <c r="H11" t="n">
-        <v>3609.870372125369</v>
+        <v>2031.038689481178</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9311727832970746</v>
+        <v>0.6512663238117208</v>
       </c>
       <c r="J11" t="n">
-        <v>-1280.163791171107</v>
+        <v>-1316.302789080456</v>
       </c>
       <c r="K11" t="n">
-        <v>-1274.491227357204</v>
+        <v>-1296.448815731796</v>
       </c>
     </row>
     <row r="12">
@@ -882,36 +882,36 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>P, Plag1</t>
+          <t>t, t_ind_ad, V_calc, dXdt_calc</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-2.43123429265257</v>
+        <v>-0.5321010750037467</v>
       </c>
       <c r="E12" t="n">
-        <v>0.008871791591213084</v>
+        <v>0.004779210422079244</v>
       </c>
       <c r="F12" t="n">
-        <v>8.304194989316687e-05</v>
+        <v>3.707956083738371e-05</v>
       </c>
       <c r="G12" t="n">
-        <v>0.009112735587800564</v>
+        <v>0.006089298878966585</v>
       </c>
       <c r="H12" t="n">
-        <v>4238.389887134308</v>
+        <v>2475.94886717634</v>
       </c>
       <c r="I12" t="n">
-        <v>2.060856834321392</v>
+        <v>0.9233125563874205</v>
       </c>
       <c r="J12" t="n">
-        <v>-1179.916746838693</v>
+        <v>-1277.508027284584</v>
       </c>
       <c r="K12" t="n">
-        <v>-1174.24418302479</v>
+        <v>-1266.162899656778</v>
       </c>
     </row>
   </sheetData>

--- a/results/feature_selection/global/wrapper/qP_calc/metrics_global.xlsx
+++ b/results/feature_selection/global/wrapper/qP_calc/metrics_global.xlsx
@@ -492,120 +492,120 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>t, t_ind, t_ind_ad, T, I, X_calc, V_calc, dXdt_calc, Xlag1_calc</t>
+          <t>t, t_ind_ad, T, I, FS_calc, X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.810998545093071</v>
+        <v>0.8290025398251308</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0007234786044292191</v>
+        <v>0.0006831911499731838</v>
       </c>
       <c r="F2" t="n">
-        <v>4.574170111823968e-06</v>
+        <v>4.138441536944064e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>0.002138730958260989</v>
+        <v>0.002034315987486719</v>
       </c>
       <c r="H2" t="n">
-        <v>520.1446837301559</v>
+        <v>541.7875783530312</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06120363839115698</v>
+        <v>0.05680213496153661</v>
       </c>
       <c r="J2" t="n">
-        <v>-1531.180744273729</v>
+        <v>-1539.794101450123</v>
       </c>
       <c r="K2" t="n">
-        <v>-1505.654207111166</v>
+        <v>-1508.595000473657</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>tweedie</t>
+          <t>rf_b</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>t_ind, t_ind_ad, I, X_calc</t>
+          <t>t</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.8065244737030708</v>
+        <v>0.7514262365591471</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00085980535804047</v>
+        <v>0.0009613133731027966</v>
       </c>
       <c r="F3" t="n">
-        <v>4.68245056733889e-06</v>
+        <v>6.015925538111114e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002163897078730615</v>
+        <v>0.002452738375390069</v>
       </c>
       <c r="H3" t="n">
-        <v>669.6561486172901</v>
+        <v>447.5506557366535</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06004593560447592</v>
+        <v>0.07507634018013255</v>
       </c>
       <c r="J3" t="n">
-        <v>-1538.232808906948</v>
+        <v>-1512.658643936451</v>
       </c>
       <c r="K3" t="n">
-        <v>-1526.887681279142</v>
+        <v>-1509.8223620295</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>poisson</t>
+          <t>tweedie</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>t_ind_ad, T, I, V_calc</t>
+          <t>t, t_ind_ad, I, FS_calc, X_calc, dVdt_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.4237192234819377</v>
+        <v>0.652309038630559</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001426906154968586</v>
+        <v>0.0009911320897953361</v>
       </c>
       <c r="F4" t="n">
-        <v>1.394701593839947e-05</v>
+        <v>8.414737359723534e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003734570382038538</v>
+        <v>0.002900816671167541</v>
       </c>
       <c r="H4" t="n">
-        <v>1175.907142576187</v>
+        <v>730.7773552188963</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1748939958665756</v>
+        <v>0.1078131787269841</v>
       </c>
       <c r="J4" t="n">
-        <v>-1400.710867959432</v>
+        <v>-1458.37626866356</v>
       </c>
       <c r="K4" t="n">
-        <v>-1389.365740331626</v>
+        <v>-1438.5222953149</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>rf_b</t>
+          <t>poisson</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -613,110 +613,110 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>t, t_ind, t_ind_ad, mu_calc</t>
+          <t>t_ind_ad, T, I, V_calc</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.3630792019840874</v>
+        <v>0.4237192234819377</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001207449833222983</v>
+        <v>0.001426906154968586</v>
       </c>
       <c r="F5" t="n">
-        <v>1.541461191035863e-05</v>
+        <v>1.394701593839947e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003926144662433954</v>
+        <v>0.003734570382038538</v>
       </c>
       <c r="H5" t="n">
-        <v>626.9897101231327</v>
+        <v>1175.907142576187</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1930870296331111</v>
+        <v>0.1748939958665756</v>
       </c>
       <c r="J5" t="n">
-        <v>-1388.104528803918</v>
+        <v>-1400.710867959432</v>
       </c>
       <c r="K5" t="n">
-        <v>-1376.759401176112</v>
+        <v>-1389.365740331626</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ridge_b</t>
+          <t>elasticnet_b</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>t, t_ind, t_ind_ad, X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc</t>
+          <t>t, t_ind_ad, X_calc, V_calc, mu_calc, dXdt_calc</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.3614793866229301</v>
+        <v>0.325061675359731</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002345261003869446</v>
+        <v>0.002335111253905205</v>
       </c>
       <c r="F6" t="n">
-        <v>1.545333027690796e-05</v>
+        <v>1.633470342021625e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003931072407996062</v>
+        <v>0.004041621385065188</v>
       </c>
       <c r="H6" t="n">
-        <v>1152.11648947025</v>
+        <v>1204.578055301676</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1955670013443148</v>
+        <v>0.2054929316844749</v>
       </c>
       <c r="J6" t="n">
-        <v>-1379.788439269078</v>
+        <v>-1376.799552315338</v>
       </c>
       <c r="K6" t="n">
-        <v>-1357.098184013467</v>
+        <v>-1359.781860873629</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>elasticnet_b</t>
+          <t>Ridge_b</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>t_ind, t_ind_ad, X_calc, V_calc, mu_calc, dXdt_calc</t>
+          <t>t, t_ind_ad, T, V_calc</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.3402792871388413</v>
+        <v>0.3176571949726961</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002287970419760139</v>
+        <v>0.002055810691995449</v>
       </c>
       <c r="F7" t="n">
-        <v>1.596641025015772e-05</v>
+        <v>1.651390496602784e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.003995799075298672</v>
+        <v>0.00406373042487169</v>
       </c>
       <c r="H7" t="n">
-        <v>1016.330923072539</v>
+        <v>960.9678268309061</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2009273903455228</v>
+        <v>0.2067144012416674</v>
       </c>
       <c r="J7" t="n">
-        <v>-1379.672948631027</v>
+        <v>-1379.424783648919</v>
       </c>
       <c r="K7" t="n">
-        <v>-1362.655257189318</v>
+        <v>-1368.079656021113</v>
       </c>
     </row>
     <row r="8">
@@ -800,79 +800,79 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>svm_rbf</t>
+          <t>svm_linear</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>t, t_ind_ad</t>
+          <t>t, t_ind_ad, mu_calc</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.007699272210740071</v>
+        <v>0.002389929643822564</v>
       </c>
       <c r="E10" t="n">
-        <v>0.003591133369350678</v>
+        <v>0.003574552768128984</v>
       </c>
       <c r="F10" t="n">
-        <v>2.438810799061286e-05</v>
+        <v>2.414393142806721e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.004938431733922507</v>
+        <v>0.004913647466807851</v>
       </c>
       <c r="H10" t="n">
-        <v>2799.88878686078</v>
+        <v>2054.878777741465</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6066537066776311</v>
+        <v>0.300799921858853</v>
       </c>
       <c r="J10" t="n">
-        <v>-1334.298280160157</v>
+        <v>-1333.566164504309</v>
       </c>
       <c r="K10" t="n">
-        <v>-1328.625716346254</v>
+        <v>-1325.057318783454</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>svm_linear</t>
+          <t>svm_rbf</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>t, t_ind, t_ind_ad, X_calc, V_calc, mu_calc, Xlag1_calc</t>
+          <t>t, t_ind_ad</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.07371657271770093</v>
+        <v>-0.007699272210740071</v>
       </c>
       <c r="E11" t="n">
-        <v>0.003893150879675575</v>
+        <v>0.003591133369350678</v>
       </c>
       <c r="F11" t="n">
-        <v>2.598584364291746e-05</v>
+        <v>2.438810799061286e-05</v>
       </c>
       <c r="G11" t="n">
-        <v>0.005097631179569336</v>
+        <v>0.004938431733922507</v>
       </c>
       <c r="H11" t="n">
-        <v>2031.038689481178</v>
+        <v>2799.88878686078</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6512663238117208</v>
+        <v>0.6066537066776311</v>
       </c>
       <c r="J11" t="n">
-        <v>-1316.302789080456</v>
+        <v>-1334.298280160157</v>
       </c>
       <c r="K11" t="n">
-        <v>-1296.448815731796</v>
+        <v>-1328.625716346254</v>
       </c>
     </row>
     <row r="12">
@@ -882,36 +882,36 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>t, t_ind_ad, V_calc, dXdt_calc</t>
+          <t>t, t_ind_ad, X_calc, V_calc, dXdt_calc, dVdt_calc</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.5321010750037467</v>
+        <v>-0.3506861557324688</v>
       </c>
       <c r="E12" t="n">
-        <v>0.004779210422079244</v>
+        <v>0.004656388419575724</v>
       </c>
       <c r="F12" t="n">
-        <v>3.707956083738371e-05</v>
+        <v>3.268899833098252e-05</v>
       </c>
       <c r="G12" t="n">
-        <v>0.006089298878966585</v>
+        <v>0.005717429346391831</v>
       </c>
       <c r="H12" t="n">
-        <v>2475.94886717634</v>
+        <v>2215.798057115956</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9233125563874205</v>
+        <v>0.8164574580371448</v>
       </c>
       <c r="J12" t="n">
-        <v>-1277.508027284584</v>
+        <v>-1289.387469372665</v>
       </c>
       <c r="K12" t="n">
-        <v>-1266.162899656778</v>
+        <v>-1272.369777930956</v>
       </c>
     </row>
   </sheetData>
